--- a/data/predictions/2026-04-06_ST.xlsx
+++ b/data/predictions/2026-04-06_ST.xlsx
@@ -541,12 +541,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>1</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -558,8 +562,10 @@
           <t>ALMIGHTY LIGHTNING</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>5</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -576,47 +582,79 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>10</v>
-      </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.5902</v>
-      </c>
-      <c r="R2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="S2" t="n">
-        <v>7.9</v>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5.5902</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="n">
-        <v>2</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -628,8 +666,10 @@
           <t>INVICTUS</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -646,47 +686,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>5</v>
-      </c>
-      <c r="O3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.4012</v>
-      </c>
-      <c r="R3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9.6</v>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5.4012</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
       </c>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="n">
-        <v>3</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -698,8 +770,10 @@
           <t>CASA BUDDY</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>3</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -716,47 +790,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.376</v>
-      </c>
-      <c r="R4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="S4" t="n">
-        <v>9.800000000000001</v>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5.376</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
       </c>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="n">
-        <v>4</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -768,8 +874,10 @@
           <t>MEGA CAPTAIN</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>4</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -786,47 +894,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5.3571</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5.3571</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -838,8 +978,10 @@
           <t>MAJESTIC DELIGHT</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>3</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -856,47 +998,79 @@
           <t>1/2/5/9/3/2</t>
         </is>
       </c>
-      <c r="J6" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>9.217391304347826</v>
-      </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6.1099</v>
-      </c>
-      <c r="R6" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.1</v>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>9.217391304347826</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>6.1099</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>20.8</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
       </c>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="n">
-        <v>2</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -908,8 +1082,10 @@
           <t>KING ALLOY</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>7</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -926,47 +1102,79 @@
           <t>3/3/6/6/3/6</t>
         </is>
       </c>
-      <c r="J7" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="K7" t="n">
-        <v>7</v>
-      </c>
-      <c r="L7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" t="n">
-        <v>8.434782608695652</v>
-      </c>
-      <c r="P7" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5.6104</v>
-      </c>
-      <c r="R7" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>6.7</v>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5.52</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>8.434782608695652</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5.6104</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>3</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -978,8 +1186,10 @@
           <t>ALWAYS FLUKE</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>8</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -996,47 +1206,79 @@
           <t>6/3/2/6/10/9</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P8" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.2192</v>
-      </c>
-      <c r="R8" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3.81</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5.2192</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>4</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1048,8 +1290,10 @@
           <t>LUCKY GENERATIONS</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>13</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1066,47 +1310,79 @@
           <t>1/7/11/1/4/13</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>8.043478260869566</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.2046</v>
-      </c>
-      <c r="R9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10.1</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5.88</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>8.043478260869566</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5.2046</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
       </c>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>3</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1118,8 +1394,10 @@
           <t>MR COOL</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>8</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1136,47 +1414,79 @@
           <t>3/4/3/3/11/5</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.6336</v>
-      </c>
-      <c r="R10" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5.2</v>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5.6336</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>16.4</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
       </c>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>3</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
-        <v>2</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1188,8 +1498,10 @@
           <t>SMART FAT CAT</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>9</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1206,47 +1518,79 @@
           <t>5/9/5/3/2/7</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.2654</v>
-      </c>
-      <c r="R11" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>7.5</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5.67</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5.2654</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>11.4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
       </c>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
-        <v>3</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1258,8 +1602,10 @@
           <t>AMAZING GAZE</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>11</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1276,47 +1622,79 @@
           <t>8/3/8/3/4/8</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="K12" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.1996</v>
-      </c>
-      <c r="R12" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="S12" t="n">
-        <v>8</v>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5.1996</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>3</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>4</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1328,8 +1706,10 @@
           <t>LUCKY YEAR</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>6</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1346,47 +1726,79 @@
           <t>6/4/7</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.0512</v>
-      </c>
-      <c r="R13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="S13" t="n">
-        <v>9.199999999999999</v>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4.17</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5.0512</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
       </c>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>4</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1398,8 +1810,10 @@
           <t>LUCKY RANGER</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>8</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1416,47 +1830,79 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>10</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>6.7648</v>
-      </c>
-      <c r="R14" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.8</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9.33</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6.7648</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2.8</t>
+        </is>
       </c>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>2</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1468,8 +1914,10 @@
           <t>GALLANT EPOCH</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>5</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1486,47 +1934,79 @@
           <t>3/2/1/2/10/3</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>10</v>
-      </c>
-      <c r="P15" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>6.1222</v>
-      </c>
-      <c r="R15" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5.4</v>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6.1222</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
       </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>4</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>3</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1538,8 +2018,10 @@
           <t>ROBOT STAR</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>7</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1556,47 +2038,79 @@
           <t>5/2/1/8/4</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5</v>
-      </c>
-      <c r="O16" t="n">
-        <v>9.470588235294118</v>
-      </c>
-      <c r="P16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.8275</v>
-      </c>
-      <c r="R16" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>7.2</v>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6.07</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>9.470588235294118</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5.8275</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>4</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>4</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1608,8 +2122,10 @@
           <t>CLEANSWEEPER</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>9</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1626,47 +2142,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="L17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>5.764705882352941</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.2433</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="S17" t="n">
-        <v>12.9</v>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6.72</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>5.764705882352941</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5.2433</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
       </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>5</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1678,8 +2226,10 @@
           <t>RIDING HIGH</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>2</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1696,47 +2246,79 @@
           <t>4/3/5/1/2/2</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>8.380000000000001</v>
-      </c>
-      <c r="K18" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="L18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5.9696</v>
-      </c>
-      <c r="R18" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>6</v>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7.98</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>5.9696</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>14.2</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>5</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="n">
-        <v>2</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1748,8 +2330,10 @@
           <t>THOUSAND SPIRIT</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>8</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1766,47 +2350,79 @@
           <t>9/2/4/3/12/3</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>9.4375</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.7538</v>
-      </c>
-      <c r="R19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="S19" t="n">
-        <v>7.4</v>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>5.86</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>9.4375</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5.7538</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
       </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>5</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>3</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1818,8 +2434,10 @@
           <t>MR INCREDIBLE</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>4</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1836,47 +2454,79 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M20" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>10</v>
-      </c>
-      <c r="P20" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>5.6091</v>
-      </c>
-      <c r="R20" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="S20" t="n">
-        <v>8.6</v>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5.6091</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>5</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>4</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1888,8 +2538,10 @@
           <t>LUCRATIVE EIGHT</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>3</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1906,47 +2558,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5</v>
-      </c>
-      <c r="O21" t="n">
-        <v>6.0625</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.3524</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="S21" t="n">
-        <v>11</v>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>6.0625</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5.3524</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>6</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1958,8 +2642,10 @@
           <t>GLOWING PRAISES</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>11</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1976,47 +2662,79 @@
           <t>3/5/1</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>10</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6.342</v>
-      </c>
-      <c r="R22" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.7</v>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6.342</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>23.1</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>6</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>2</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2028,8 +2746,10 @@
           <t>FAST RESPONDER</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>8</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2046,47 +2766,79 @@
           <t>4/5/5/2/2/2</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M23" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5</v>
-      </c>
-      <c r="O23" t="n">
-        <v>6.294117647058823</v>
-      </c>
-      <c r="P23" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>6.105</v>
-      </c>
-      <c r="R23" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.7</v>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>6.294117647058823</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6.105</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
       </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>6</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="n">
-        <v>3</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2098,8 +2850,10 @@
           <t>KANSAS</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2116,47 +2870,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>7.352941176470588</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.4931</v>
-      </c>
-      <c r="R24" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="S24" t="n">
-        <v>8.6</v>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>7.352941176470588</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5.4931</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
       </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>6</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>4</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2168,8 +2954,10 @@
           <t>ALPHA STRIKE</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>4</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2186,47 +2974,79 @@
           <t>4/10/12/1</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K25" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>5.764705882352941</v>
-      </c>
-      <c r="P25" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5.3406</v>
-      </c>
-      <c r="R25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>5.764705882352941</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>5.3406</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>7</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2238,8 +3058,10 @@
           <t>KA YING RISING</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>5</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2256,47 +3078,79 @@
           <t>1/1/1/1/1/1</t>
         </is>
       </c>
-      <c r="J26" t="n">
-        <v>10</v>
-      </c>
-      <c r="K26" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>10</v>
-      </c>
-      <c r="P26" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6.9902</v>
-      </c>
-      <c r="R26" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.9</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>6.9902</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1.9</t>
+        </is>
       </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>7</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>2</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2308,8 +3162,10 @@
           <t>HELIOS EXPRESS</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>4</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -2326,47 +3182,79 @@
           <t>2/2/5/3/5/1</t>
         </is>
       </c>
-      <c r="J27" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="K27" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M27" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>5.371428571428571</v>
-      </c>
-      <c r="P27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>6.1796</v>
-      </c>
-      <c r="R27" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.2</v>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>7.57</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>5.371428571428571</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>6.1796</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
       </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>7</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
-        <v>3</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2378,8 +3266,10 @@
           <t>RAGING BLIZZARD</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>7</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2396,47 +3286,79 @@
           <t>5/4/2/5/2/2</t>
         </is>
       </c>
-      <c r="J28" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="K28" t="n">
-        <v>7</v>
-      </c>
-      <c r="L28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3.057142857142857</v>
-      </c>
-      <c r="P28" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>5.9341</v>
-      </c>
-      <c r="R28" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="S28" t="n">
-        <v>5.4</v>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>3.057142857142857</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>5.9341</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
       </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
-        <v>4</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2448,8 +3370,10 @@
           <t>STELLAR EXPRESS</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>6</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2466,47 +3390,79 @@
           <t>6/1/1/1/14/8</t>
         </is>
       </c>
-      <c r="J29" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="K29" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.0288</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>13.3</v>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5.29</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>7.14</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>5.0288</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2518,8 +3474,10 @@
           <t>FIT FOR BEAUTY</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>7</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2536,47 +3494,79 @@
           <t>1/9/6/1/2/1</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="K30" t="n">
-        <v>7</v>
-      </c>
-      <c r="L30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M30" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N30" t="n">
-        <v>5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>7.230769230769231</v>
-      </c>
-      <c r="P30" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.2504</v>
-      </c>
-      <c r="R30" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4.3</v>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>8.14</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>7.230769230769231</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>6.2504</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>19.6</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>8</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>2</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -2588,8 +3578,10 @@
           <t>THE RED HARE</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>4</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2606,47 +3598,79 @@
           <t>3/2/6/3/1/3</t>
         </is>
       </c>
-      <c r="J31" t="n">
-        <v>8</v>
-      </c>
-      <c r="K31" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" t="n">
-        <v>6.538461538461538</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6.2068</v>
-      </c>
-      <c r="R31" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4.5</v>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>6.538461538461538</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>6.2068</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
       </c>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>8</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>3</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2658,8 +3682,10 @@
           <t>MIGHTY MASTS</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>10</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2676,47 +3702,79 @@
           <t>2/6/6/2</t>
         </is>
       </c>
-      <c r="J32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N32" t="n">
-        <v>5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>9.307692307692308</v>
-      </c>
-      <c r="P32" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5.8924</v>
-      </c>
-      <c r="R32" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="S32" t="n">
-        <v>6.2</v>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>9.307692307692308</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>5.8924</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>13.7</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
       </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>8</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
-        <v>4</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2728,8 +3786,10 @@
           <t>PACKING GLORY</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>3</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2746,47 +3806,79 @@
           <t>3/3/2/5/1</t>
         </is>
       </c>
-      <c r="J33" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="K33" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5.8576</v>
-      </c>
-      <c r="R33" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>6.4</v>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>8.07</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>5.8576</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>13.3</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
       </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>9</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2798,8 +3890,10 @@
           <t>FAST NETWORK</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>11</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2816,47 +3910,79 @@
           <t>1/3/3/2/6/1</t>
         </is>
       </c>
-      <c r="J34" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="L34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>6.399</v>
-      </c>
-      <c r="R34" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="S34" t="n">
-        <v>5.8</v>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>6.399</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>14.7</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
       </c>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>9</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>2</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2868,8 +3994,10 @@
           <t>MY WISH</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>4</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2886,47 +4014,79 @@
           <t>4/4/6/4/1/1</t>
         </is>
       </c>
-      <c r="J35" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="K35" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>6.3709</v>
-      </c>
-      <c r="R35" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5.9</v>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>7.81</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>6.3709</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>14.3</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
       </c>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>9</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
-        <v>3</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2938,8 +4098,10 @@
           <t>VOYAGE BUBBLE</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>3</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2956,47 +4118,79 @@
           <t>5/3/1/2/12/1</t>
         </is>
       </c>
-      <c r="J36" t="n">
-        <v>7.24</v>
-      </c>
-      <c r="K36" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="L36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="n">
-        <v>10</v>
-      </c>
-      <c r="P36" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>6.2552</v>
-      </c>
-      <c r="R36" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6.6</v>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>7.24</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>6.2552</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
       </c>
       <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>4</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3008,8 +4202,10 @@
           <t>LUCKY SWEYNESSE</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>10</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3026,47 +4222,79 @@
           <t>3/2/4/4/11/2</t>
         </is>
       </c>
-      <c r="J37" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="K37" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N37" t="n">
-        <v>5</v>
-      </c>
-      <c r="O37" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="P37" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>5.8999</v>
-      </c>
-      <c r="R37" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="S37" t="n">
-        <v>9.6</v>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>6.05</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>5.8999</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>9.6</t>
+        </is>
       </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>10</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>1</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3078,8 +4306,10 @@
           <t>NEW FOREST</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>7</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3096,47 +4326,79 @@
           <t>11/8/1/1/4/1</t>
         </is>
       </c>
-      <c r="J38" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="K38" t="n">
-        <v>7</v>
-      </c>
-      <c r="L38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="P38" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>6.2083</v>
-      </c>
-      <c r="R38" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.2</v>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>7.86</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>7.75</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>6.2083</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
       </c>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>10</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
-        <v>2</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3148,8 +4410,10 @@
           <t>WINNING OVATION</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>8</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3166,47 +4430,79 @@
           <t>1/1/1/8</t>
         </is>
       </c>
-      <c r="J39" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K39" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M39" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N39" t="n">
-        <v>5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>7</v>
-      </c>
-      <c r="P39" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>5.8464</v>
-      </c>
-      <c r="R39" t="n">
-        <v>14</v>
-      </c>
-      <c r="S39" t="n">
-        <v>6.1</v>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>5.8464</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
       </c>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>10</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
-        <v>3</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3218,8 +4514,10 @@
           <t>STEPS AHEAD</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>10</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -3236,47 +4534,79 @@
           <t>12/5/3/5/2/2</t>
         </is>
       </c>
-      <c r="J40" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="K40" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N40" t="n">
-        <v>5</v>
-      </c>
-      <c r="O40" t="n">
-        <v>4</v>
-      </c>
-      <c r="P40" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>5.7533</v>
-      </c>
-      <c r="R40" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="S40" t="n">
-        <v>6.6</v>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>7.33</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5.7533</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
       </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>10</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
-        <v>4</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3288,8 +4618,10 @@
           <t>SIX PACK</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>1</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -3306,47 +4638,79 @@
           <t>2/4/2/1/4/6</t>
         </is>
       </c>
-      <c r="J41" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="K41" t="n">
-        <v>8.26</v>
-      </c>
-      <c r="L41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>5</v>
-      </c>
-      <c r="O41" t="n">
-        <v>4</v>
-      </c>
-      <c r="P41" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>5.7512</v>
-      </c>
-      <c r="R41" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="S41" t="n">
-        <v>6.7</v>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6.76</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>5.7512</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>12.7</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
       </c>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>11</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>1</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3358,8 +4722,10 @@
           <t>MONEY CATCHER</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>10</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -3376,47 +4742,79 @@
           <t>3/3/7/3/1/3</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="K42" t="n">
-        <v>6.51</v>
-      </c>
-      <c r="L42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P42" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>5.9157</v>
-      </c>
-      <c r="R42" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="S42" t="n">
-        <v>5.5</v>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>7.76</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>6.51</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>5.9157</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
       </c>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>11</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>2</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3428,8 +4826,10 @@
           <t>SMART AVENUE</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>8</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -3446,47 +4846,79 @@
           <t>2/2/8/2/1/4</t>
         </is>
       </c>
-      <c r="J43" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="K43" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="L43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>5.8828</v>
-      </c>
-      <c r="R43" t="n">
-        <v>15</v>
-      </c>
-      <c r="S43" t="n">
-        <v>5.7</v>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5.8828</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
       </c>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>11</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>3</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3498,8 +4930,10 @@
           <t>LIVEANDLETLIVE</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>4</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -3516,47 +4950,79 @@
           <t>4/12/2/2/10/2</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="K44" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="L44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N44" t="n">
-        <v>5</v>
-      </c>
-      <c r="O44" t="n">
-        <v>7</v>
-      </c>
-      <c r="P44" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>5.7323</v>
-      </c>
-      <c r="R44" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="S44" t="n">
-        <v>6.6</v>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>7.49</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5.7323</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
       </c>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>11</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
-        <v>4</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3568,8 +5034,10 @@
           <t>THE AUSPICIOUS</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>5</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3586,39 +5054,67 @@
           <t>9/5/7/4/3/1</t>
         </is>
       </c>
-      <c r="J45" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K45" t="n">
-        <v>7.28</v>
-      </c>
-      <c r="L45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M45" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N45" t="n">
-        <v>5</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>5.5342</v>
-      </c>
-      <c r="R45" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="S45" t="n">
-        <v>8</v>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>7.28</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>5.5342</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>10.6</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3797,7 +5293,6 @@
           <t>1/9/6/1/2/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.140000000000001</v>
       </c>
@@ -3878,7 +5373,6 @@
           <t>3/2/6/3/1/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>8</v>
       </c>
@@ -3959,7 +5453,6 @@
           <t>2/6/6/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.5</v>
       </c>
@@ -4040,7 +5533,6 @@
           <t>3/3/2/5/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>8.07</v>
       </c>
@@ -4121,7 +5613,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -4202,7 +5693,6 @@
           <t>7/9/9/2/8/6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>3.95</v>
       </c>
@@ -4283,7 +5773,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -4364,7 +5853,6 @@
           <t>5/3/5/5/4/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.67</v>
       </c>
@@ -4445,7 +5933,6 @@
           <t>10/13/14/2/10/7</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3.1</v>
       </c>
@@ -4526,7 +6013,6 @@
           <t>13/10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1</v>
       </c>
@@ -4738,7 +6224,6 @@
           <t>1/3/3/2/6/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.9</v>
       </c>
@@ -4819,7 +6304,6 @@
           <t>4/4/6/4/1/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.81</v>
       </c>
@@ -4900,7 +6384,6 @@
           <t>5/3/1/2/12/1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.24</v>
       </c>
@@ -4981,7 +6464,6 @@
           <t>3/2/4/4/11/2</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.05</v>
       </c>
@@ -5062,7 +6544,6 @@
           <t>-/8/2/3/5/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>7.1</v>
       </c>
@@ -5143,7 +6624,6 @@
           <t>4/7/5/1/6/5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.57</v>
       </c>
@@ -5224,7 +6704,6 @@
           <t>5/8/1/3/7/5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5.52</v>
       </c>
@@ -5305,7 +6784,6 @@
           <t>5/7/7/1/1/7</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>6.1</v>
       </c>
@@ -5386,7 +6864,6 @@
           <t>7/4/13/2/4/11</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.29</v>
       </c>
@@ -5467,7 +6944,6 @@
           <t>5/7/6/7/12/2</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>4.48</v>
       </c>
@@ -5548,7 +7024,6 @@
           <t>1/1/9/2/11/3</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>5.95</v>
       </c>
@@ -5629,7 +7104,6 @@
           <t>10/10/9/5/2/6</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>4.67</v>
       </c>
@@ -5710,7 +7184,6 @@
           <t>9/9/3/12/10/6</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>3</v>
       </c>
@@ -5791,7 +7264,6 @@
           <t>6/6/6/8/8/7</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2.86</v>
       </c>
@@ -6003,7 +7475,6 @@
           <t>11/8/1/1/4/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.86</v>
       </c>
@@ -6084,7 +7555,6 @@
           <t>1/1/1/8</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.8</v>
       </c>
@@ -6165,7 +7635,6 @@
           <t>12/5/3/5/2/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.33</v>
       </c>
@@ -6246,7 +7715,6 @@
           <t>2/4/2/1/4/6</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.76</v>
       </c>
@@ -6327,7 +7795,6 @@
           <t>7/4/6/6/9/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.38</v>
       </c>
@@ -6408,7 +7875,6 @@
           <t>13/4/2/10/2/6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.38</v>
       </c>
@@ -6489,7 +7955,6 @@
           <t>8/8/9/8/1/6</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.48</v>
       </c>
@@ -6570,7 +8035,6 @@
           <t>11/11/12/8/7/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.52</v>
       </c>
@@ -6651,7 +8115,6 @@
           <t>11/8/1/6/5/9</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.19</v>
       </c>
@@ -6732,7 +8195,6 @@
           <t>11/3/10/8/10/13</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.86</v>
       </c>
@@ -6944,7 +8406,6 @@
           <t>3/3/7/3/1/3</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>7.76</v>
       </c>
@@ -7025,7 +8486,6 @@
           <t>2/2/8/2/1/4</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.38</v>
       </c>
@@ -7106,7 +8566,6 @@
           <t>4/12/2/2/10/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.19</v>
       </c>
@@ -7187,7 +8646,6 @@
           <t>9/5/7/4/3/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>6.9</v>
       </c>
@@ -7268,7 +8726,6 @@
           <t>4/9/5/10/4/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5.67</v>
       </c>
@@ -7349,7 +8806,6 @@
           <t>10/4/11/2/5</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.13</v>
       </c>
@@ -7430,7 +8886,6 @@
           <t>11/8/2/4/6/8</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.19</v>
       </c>
@@ -7511,7 +8966,6 @@
           <t>4/2/4/10/7/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.05</v>
       </c>
@@ -7592,7 +9046,6 @@
           <t>1/11/9/8/5/9</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>3</v>
       </c>
@@ -7673,7 +9126,6 @@
           <t>6/13/8/1/10/9</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>3.29</v>
       </c>
@@ -7754,7 +9206,6 @@
           <t>11/7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.33</v>
       </c>
@@ -7939,7 +9390,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>1</t>
@@ -8041,7 +9491,6 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>5</t>
@@ -8143,7 +9592,6 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>1</t>
@@ -8245,7 +9693,6 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>2</t>
@@ -8347,7 +9794,6 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>14</t>
@@ -8449,7 +9895,6 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>1</t>
@@ -8551,7 +9996,6 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>1</t>
@@ -8653,7 +10097,6 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>4</t>
@@ -8755,7 +10198,6 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>5</t>
@@ -8857,7 +10299,6 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>2</t>
@@ -8959,7 +10400,6 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>8</t>
@@ -9234,7 +10674,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5</v>
       </c>
@@ -9315,7 +10754,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5</v>
       </c>
@@ -9396,7 +10834,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -9477,7 +10914,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
@@ -9558,7 +10994,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -9639,7 +11074,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -9720,7 +11154,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -9801,7 +11234,6 @@
           <t>8/5/4/2/6/9</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>4.67</v>
       </c>
@@ -9882,7 +11314,6 @@
           <t>9/6/4/4/6/5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.86</v>
       </c>
@@ -9963,7 +11394,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5</v>
       </c>
@@ -10044,7 +11474,6 @@
           <t>11/4</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>4.33</v>
       </c>
@@ -10210,7 +11639,6 @@
           <t>12/13/8/5/3/11</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>3.57</v>
       </c>
@@ -10291,7 +11719,6 @@
           <t>4/7/6/7/7/11</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>2.71</v>
       </c>
@@ -10503,7 +11930,6 @@
           <t>1/2/5/9/3/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>6.9</v>
       </c>
@@ -10584,7 +12010,6 @@
           <t>3/3/6/6/3/6</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.52</v>
       </c>
@@ -10665,7 +12090,6 @@
           <t>6/3/2/6/10/9</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>3.81</v>
       </c>
@@ -10746,7 +12170,6 @@
           <t>1/7/11/1/4/13</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.52</v>
       </c>
@@ -10827,7 +12250,6 @@
           <t>9/14/11/6/11/3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>3.62</v>
       </c>
@@ -10908,7 +12330,6 @@
           <t>6/3/11/10/6/8</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2.81</v>
       </c>
@@ -10989,7 +12410,6 @@
           <t>5/2/9/6/4/9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.14</v>
       </c>
@@ -11070,7 +12490,6 @@
           <t>6/8/5/5/8/12</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.81</v>
       </c>
@@ -11151,7 +12570,6 @@
           <t>12/8/4/10/10/14</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>1.81</v>
       </c>
@@ -11232,7 +12650,6 @@
           <t>12/14/4/11/12/11</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>1.71</v>
       </c>
@@ -11313,7 +12730,6 @@
           <t>5/5/6/7/12/12</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.38</v>
       </c>
@@ -11564,7 +12980,6 @@
           <t>10/9/10/10/12/9</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1.38</v>
       </c>
@@ -11776,7 +13191,6 @@
           <t>3/4/3/3/11/5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>5.29</v>
       </c>
@@ -11857,7 +13271,6 @@
           <t>5/9/5/3/2/7</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.67</v>
       </c>
@@ -11938,7 +13351,6 @@
           <t>8/3/8/3/4/8</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>4.67</v>
       </c>
@@ -12019,7 +13431,6 @@
           <t>6/4/7</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>4.17</v>
       </c>
@@ -12100,7 +13511,6 @@
           <t>11/3/10/5/3/14</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.1</v>
       </c>
@@ -12181,7 +13591,6 @@
           <t>7/1/7/10/3/4</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5.33</v>
       </c>
@@ -12262,7 +13671,6 @@
           <t>4/3/4/5/9/6</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.48</v>
       </c>
@@ -12343,7 +13751,6 @@
           <t>5/5/8/11</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.5</v>
       </c>
@@ -12424,7 +13831,6 @@
           <t>12/4/6/8/10</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.53</v>
       </c>
@@ -12505,7 +13911,6 @@
           <t>7/10/14/11/4/9</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.57</v>
       </c>
@@ -12586,7 +13991,6 @@
           <t>4/9/7/11/10/6</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>2.48</v>
       </c>
@@ -12667,7 +14071,6 @@
           <t>4/11/12/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.5</v>
       </c>
@@ -12748,7 +14151,6 @@
           <t>11/9/9/13/13</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>1.33</v>
       </c>
@@ -12960,7 +14362,6 @@
           <t>1/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>9.33</v>
       </c>
@@ -13041,7 +14442,6 @@
           <t>3/2/1/2/10/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>6.9</v>
       </c>
@@ -13122,7 +14522,6 @@
           <t>5/2/1/8/4</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>6.07</v>
       </c>
@@ -13203,7 +14602,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
@@ -13284,7 +14682,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -13365,7 +14762,6 @@
           <t>5/2/3/4/10/6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>4.76</v>
       </c>
@@ -13446,7 +14842,6 @@
           <t>8/11/11/5/2/11</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>3.71</v>
       </c>
@@ -13527,7 +14922,6 @@
           <t>12/4/9/9/11/5</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>2.95</v>
       </c>
@@ -13608,7 +15002,6 @@
           <t>11/9/6</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>2.83</v>
       </c>
@@ -13689,7 +15082,6 @@
           <t>6/1/4/14/14/12</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.71</v>
       </c>
@@ -13855,7 +15247,6 @@
           <t>10/14/12/14/6/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.71</v>
       </c>
@@ -13936,7 +15327,6 @@
           <t>13/6/10/7/9/9</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>2.19</v>
       </c>
@@ -14017,7 +15407,6 @@
           <t>10/13/11/11/10/11</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>1</v>
       </c>
@@ -14229,7 +15618,6 @@
           <t>4/3/5/1/2/2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8.380000000000001</v>
       </c>
@@ -14310,7 +15698,6 @@
           <t>9/2/4/3/12/3</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>5.86</v>
       </c>
@@ -14391,7 +15778,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -14472,7 +15858,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5</v>
       </c>
@@ -14553,7 +15938,6 @@
           <t>13/10/7/6/14/1</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.43</v>
       </c>
@@ -14634,7 +16018,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -14715,7 +16098,6 @@
           <t>5/6/11/4/2/9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>4.62</v>
       </c>
@@ -14796,7 +16178,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>5</v>
       </c>
@@ -14877,7 +16258,6 @@
           <t>3/5/7</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.5</v>
       </c>
@@ -14958,7 +16338,6 @@
           <t>8/9/5/6/5/2</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>5.52</v>
       </c>
@@ -15039,7 +16418,6 @@
           <t>2/1/6/3/11/6</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>4.86</v>
       </c>
@@ -15120,7 +16498,6 @@
           <t>6/9/2/10/2/10</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>4.29</v>
       </c>
@@ -15201,7 +16578,6 @@
           <t>9/6</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>3.33</v>
       </c>
@@ -15498,7 +16874,6 @@
           <t>3/5/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>8</v>
       </c>
@@ -15579,7 +16954,6 @@
           <t>4/5/5/2/2/2</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.9</v>
       </c>
@@ -15660,7 +17034,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>5</v>
       </c>
@@ -15741,7 +17114,6 @@
           <t>4/10/12/1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.1</v>
       </c>
@@ -15822,7 +17194,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>5</v>
       </c>
@@ -15903,7 +17274,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>5</v>
       </c>
@@ -15984,7 +17354,6 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>5</v>
       </c>
@@ -16065,7 +17434,6 @@
           <t>9/8/12/1/12/6</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
         <v>3.71</v>
       </c>
@@ -16146,7 +17514,6 @@
           <t>5/2/12/3/8/7</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
         <v>4.1</v>
       </c>
@@ -16227,7 +17594,6 @@
           <t>9/11/8/4/12/14</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>2.14</v>
       </c>
@@ -16308,7 +17674,6 @@
           <t>8/10/6/6/6/8</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
         <v>3.05</v>
       </c>
@@ -16389,7 +17754,6 @@
           <t>6/14/12/12</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>1.3</v>
       </c>
@@ -16601,7 +17965,6 @@
           <t>1/1/1/1/1/1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>10</v>
       </c>
@@ -16682,7 +18045,6 @@
           <t>2/2/5/3/5/1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>7.57</v>
       </c>
@@ -16763,7 +18125,6 @@
           <t>5/4/2/5/2/2</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>7.76</v>
       </c>
@@ -16844,7 +18205,6 @@
           <t>6/1/1/1/14/8</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>5.29</v>
       </c>
@@ -16925,7 +18285,6 @@
           <t>4/6/5/5/6/7</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>4.14</v>
       </c>
@@ -17006,7 +18365,6 @@
           <t>10/1/7/7/10/10</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>2.52</v>
       </c>
@@ -17087,7 +18445,6 @@
           <t>11/6/7/6/7/9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>2.9</v>
       </c>
